--- a/data/trans_camb/IMC_inf_R2-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IMC_inf_R2-Provincia-trans_camb.xlsx
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 25,69</t>
+          <t>-6,1; 25,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,78; 34,94</t>
+          <t>1,51; 34,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,93; 17,82</t>
+          <t>-15,52; 17,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-16,19; 17,8</t>
+          <t>-15,53; 20,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 30,08</t>
+          <t>-7,0; 27,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-33,77; -2,65</t>
+          <t>-33,55; -3,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 19,45</t>
+          <t>-5,72; 18,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,56; 27,19</t>
+          <t>3,21; 27,88</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-20,41; 1,56</t>
+          <t>-19,98; 3,09</t>
         </is>
       </c>
     </row>
@@ -783,54 +783,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-25,35; 139,48</t>
+          <t>-21,48; 143,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,71; 189,05</t>
+          <t>4,57; 199,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-44,4; 104,74</t>
+          <t>-46,9; 95,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-32,53; 51,74</t>
+          <t>-31,86; 59,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-11,97; 89,2</t>
+          <t>-14,73; 78,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-67,1; -5,73</t>
+          <t>-66,8; -9,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-15,82; 66,49</t>
+          <t>-14,64; 66,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,36; 92,54</t>
+          <t>7,18; 94,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-51,36; 5,44</t>
+          <t>-51,56; 10,45</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,62; 18,72</t>
+          <t>-8,53; 15,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 17,32</t>
+          <t>-6,15; 17,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-27,01; 5,11</t>
+          <t>-26,64; 4,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-13,19; 10,34</t>
+          <t>-13,54; 11,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 19,66</t>
+          <t>-6,98; 18,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-17,78; 9,15</t>
+          <t>-17,04; 9,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-8,29; 9,02</t>
+          <t>-9,05; 8,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 13,92</t>
+          <t>-4,43; 14,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-20,76; 3,05</t>
+          <t>-20,65; 3,22</t>
         </is>
       </c>
     </row>
@@ -999,54 +999,54 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-20,11; 66,37</t>
+          <t>-20,83; 51,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-17,11; 58,38</t>
+          <t>-14,87; 58,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-67,01; 13,4</t>
+          <t>-66,18; 13,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-24,03; 25,58</t>
+          <t>-24,94; 26,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-9,7; 46,97</t>
+          <t>-12,02; 42,79</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-32,75; 20,91</t>
+          <t>-32,29; 20,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-17,9; 23,48</t>
+          <t>-19,16; 22,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-8,12; 36,37</t>
+          <t>-9,71; 37,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-44,16; 7,48</t>
+          <t>-47,26; 7,5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,17; 44,19</t>
+          <t>16,03; 45,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 21,61</t>
+          <t>-5,38; 21,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 19,69</t>
+          <t>-6,82; 20,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 24,27</t>
+          <t>-1,67; 25,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-16,79; 12,1</t>
+          <t>-16,5; 10,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 26,36</t>
+          <t>-3,12; 26,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,17; 29,82</t>
+          <t>10,33; 30,44</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 11,64</t>
+          <t>-6,87; 11,93</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 19,19</t>
+          <t>-0,59; 18,74</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>51,94; 301,31</t>
+          <t>51,28; 307,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-22,76; 144,54</t>
+          <t>-23,7; 152,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-24,26; 138,73</t>
+          <t>-24,22; 135,26</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 74,27</t>
+          <t>-3,06; 77,78</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-35,23; 35,57</t>
+          <t>-34,85; 34,63</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 79,1</t>
+          <t>-7,6; 80,65</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25,06; 113,78</t>
+          <t>26,95; 116,34</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-23,14; 43,27</t>
+          <t>-20,25; 43,95</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 74,99</t>
+          <t>-1,83; 69,35</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-24,29; 3,26</t>
+          <t>-24,63; 4,75</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-17,05; 11,57</t>
+          <t>-16,25; 11,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-26,99; 3,02</t>
+          <t>-27,95; 4,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,23; 29,98</t>
+          <t>0,72; 28,94</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 25,98</t>
+          <t>-4,91; 24,61</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-26,57; 9,92</t>
+          <t>-29,29; 8,59</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 11,18</t>
+          <t>-8,32; 12,77</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-7,49; 12,87</t>
+          <t>-7,62; 13,64</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-22,66; 2,11</t>
+          <t>-21,84; 2,15</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-52,84; 11,71</t>
+          <t>-53,0; 14,83</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-37,08; 33,69</t>
+          <t>-34,73; 34,52</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-61,18; 10,14</t>
+          <t>-62,1; 16,19</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,3; 92,9</t>
+          <t>1,59; 97,6</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-11,51; 81,37</t>
+          <t>-12,22; 73,59</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-62,7; 27,35</t>
+          <t>-68,3; 23,72</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-17,95; 31,5</t>
+          <t>-19,35; 35,99</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-18,1; 35,89</t>
+          <t>-17,06; 37,4</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-51,96; 5,81</t>
+          <t>-53,62; 3,89</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-39,07; 1,61</t>
+          <t>-37,83; 1,97</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-36,76; -1,93</t>
+          <t>-37,62; 0,58</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-35,65; 0,92</t>
+          <t>-34,14; 1,17</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-32,0; 6,07</t>
+          <t>-32,83; 5,65</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-44,53; -10,08</t>
+          <t>-43,01; -7,99</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-31,84; 1,95</t>
+          <t>-34,01; 2,54</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-32,0; -3,73</t>
+          <t>-30,5; -1,88</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-36,07; -10,11</t>
+          <t>-36,47; -9,34</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-28,51; -3,47</t>
+          <t>-29,45; -3,53</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-67,87; 2,03</t>
+          <t>-62,5; 7,12</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-60,18; -3,32</t>
+          <t>-63,7; -0,93</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-56,58; 3,41</t>
+          <t>-56,43; 3,29</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-49,11; 11,13</t>
+          <t>-48,96; 11,25</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-64,31; -18,04</t>
+          <t>-62,92; -15,73</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-46,93; 3,6</t>
+          <t>-48,99; 3,55</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-50,47; -7,55</t>
+          <t>-47,84; -3,29</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-57,12; -20,24</t>
+          <t>-57,37; -18,16</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-44,89; -6,76</t>
+          <t>-46,21; -7,0</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>5,36; 36,98</t>
+          <t>4,99; 37,97</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-7,9; 22,4</t>
+          <t>-7,65; 22,11</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-12,11; 16,16</t>
+          <t>-14,02; 15,46</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-29,03; 0,83</t>
+          <t>-27,72; 2,48</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-15,65; 15,94</t>
+          <t>-14,93; 16,31</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-28,72; 2,2</t>
+          <t>-27,47; 2,06</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-8,91; 13,85</t>
+          <t>-8,81; 13,45</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-8,22; 13,8</t>
+          <t>-8,33; 14,22</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-17,4; 4,07</t>
+          <t>-17,58; 3,44</t>
         </is>
       </c>
     </row>
@@ -1863,54 +1863,54 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>13,46; 209,73</t>
+          <t>12,76; 235,08</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-27,72; 126,79</t>
+          <t>-25,73; 125,48</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-38,45; 92,41</t>
+          <t>-46,16; 94,51</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-51,65; 2,65</t>
+          <t>-49,8; 5,54</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-28,35; 37,93</t>
+          <t>-27,14; 38,38</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-50,9; 5,06</t>
+          <t>-49,42; 4,23</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-20,26; 43,08</t>
+          <t>-20,7; 41,36</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-19,45; 41,77</t>
+          <t>-19,99; 43,83</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-40,8; 12,13</t>
+          <t>-41,82; 10,5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 20,33</t>
+          <t>-0,4; 20,18</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-10,49; 8,6</t>
+          <t>-10,46; 9,61</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 14,56</t>
+          <t>-6,87; 13,91</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4,78; 25,45</t>
+          <t>4,65; 25,54</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-15,06; 5,23</t>
+          <t>-16,35; 4,58</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-11,01; 13,67</t>
+          <t>-10,14; 12,63</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,67; 19,93</t>
+          <t>4,65; 20,18</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-10,52; 3,66</t>
+          <t>-11,17; 3,97</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 11,74</t>
+          <t>-4,62; 10,93</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 80,26</t>
+          <t>-1,5; 82,17</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-31,75; 33,9</t>
+          <t>-30,33; 38,6</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-19,29; 59,75</t>
+          <t>-19,57; 56,65</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>9,53; 73,67</t>
+          <t>9,67; 72,38</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-33,99; 14,8</t>
+          <t>-35,44; 12,53</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-24,28; 39,18</t>
+          <t>-22,97; 36,1</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>12,28; 63,5</t>
+          <t>12,25; 64,87</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-26,97; 10,88</t>
+          <t>-28,51; 12,56</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-13,51; 37,18</t>
+          <t>-12,86; 33,36</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-6,46; 13,05</t>
+          <t>-6,06; 13,44</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-20,33; -0,08</t>
+          <t>-18,95; 0,64</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-30,95; -10,91</t>
+          <t>-30,15; -11,13</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 18,4</t>
+          <t>-3,63; 17,21</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-11,54; 7,98</t>
+          <t>-11,39; 9,24</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-21,36; -0,83</t>
+          <t>-21,58; -1,83</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 12,5</t>
+          <t>-2,03; 12,81</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-12,61; 1,2</t>
+          <t>-13,59; 1,43</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-23,05; -8,64</t>
+          <t>-23,21; -8,58</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-12,38; 32,91</t>
+          <t>-12,37; 31,73</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-38,76; -0,21</t>
+          <t>-37,87; 1,62</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-60,68; -26,5</t>
+          <t>-59,85; -26,25</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 42,72</t>
+          <t>-6,57; 39,7</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-22,05; 18,29</t>
+          <t>-21,73; 20,53</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-40,94; -2,35</t>
+          <t>-40,79; -3,93</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 28,58</t>
+          <t>-4,25; 29,05</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-24,84; 3,04</t>
+          <t>-26,45; 3,39</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-45,86; -20,07</t>
+          <t>-45,51; -19,46</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>2,48; 11,51</t>
+          <t>2,04; 11,6</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 4,31</t>
+          <t>-5,07; 4,02</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-12,89; -1,84</t>
+          <t>-12,44; -1,78</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>0,19; 10,03</t>
+          <t>0,19; 9,63</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 4,46</t>
+          <t>-5,29; 4,11</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-11,87; -1,14</t>
+          <t>-11,59; -1,2</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,21; 9,16</t>
+          <t>2,4; 9,1</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 2,5</t>
+          <t>-3,72; 3,11</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-10,41; -2,69</t>
+          <t>-10,27; -2,84</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>6,62; 35,38</t>
+          <t>5,64; 35,67</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-13,21; 13,13</t>
+          <t>-13,37; 12,2</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-34,68; -5,62</t>
+          <t>-33,62; -5,68</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>0,06; 22,95</t>
+          <t>0,52; 22,72</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-10,85; 10,07</t>
+          <t>-11,35; 9,58</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-25,02; -2,62</t>
+          <t>-24,39; -2,83</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>5,25; 23,49</t>
+          <t>5,61; 23,41</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-9,02; 6,44</t>
+          <t>-8,93; 7,99</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-25,15; -7,02</t>
+          <t>-24,7; -7,04</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IMC_inf_R2-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IMC_inf_R2-Provincia-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad declarado</t>
+          <t>Población con sobrepeso u obesidad declarado por los/as progenitores/as</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 25,46</t>
+          <t>-6,61; 24,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,51; 34,8</t>
+          <t>1,0; 34,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,52; 17,57</t>
+          <t>-14,09; 16,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-15,53; 20,75</t>
+          <t>-13,92; 21,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 27,74</t>
+          <t>-6,88; 28,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-33,55; -3,87</t>
+          <t>-34,19; -3,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 18,79</t>
+          <t>-5,48; 18,44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,21; 27,88</t>
+          <t>2,77; 25,72</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-19,98; 3,09</t>
+          <t>-19,76; 2,02</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-21,48; 143,4</t>
+          <t>-23,87; 123,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,57; 199,56</t>
+          <t>1,3; 181,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-46,9; 95,99</t>
+          <t>-46,66; 85,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-31,86; 59,8</t>
+          <t>-28,22; 69,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-14,73; 78,41</t>
+          <t>-14,45; 85,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-66,8; -9,91</t>
+          <t>-67,0; -9,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-14,64; 66,21</t>
+          <t>-14,0; 60,06</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,18; 94,38</t>
+          <t>6,83; 89,57</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-51,56; 10,45</t>
+          <t>-51,0; 6,92</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,53; 15,59</t>
+          <t>-8,68; 16,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 17,62</t>
+          <t>-5,72; 18,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-26,64; 4,77</t>
+          <t>-27,22; 4,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-13,54; 11,41</t>
+          <t>-13,43; 11,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 18,43</t>
+          <t>-6,28; 17,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-17,04; 9,24</t>
+          <t>-16,97; 10,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-9,05; 8,69</t>
+          <t>-8,7; 9,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 14,36</t>
+          <t>-3,07; 13,99</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-20,65; 3,22</t>
+          <t>-22,12; 2,56</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-20,83; 51,9</t>
+          <t>-20,96; 56,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-14,87; 58,19</t>
+          <t>-13,59; 64,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-66,18; 13,32</t>
+          <t>-67,22; 14,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-24,94; 26,58</t>
+          <t>-25,03; 27,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-12,02; 42,79</t>
+          <t>-11,53; 41,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-32,29; 20,75</t>
+          <t>-31,43; 23,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-19,16; 22,45</t>
+          <t>-18,35; 23,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-9,71; 37,32</t>
+          <t>-6,31; 36,38</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-47,26; 7,5</t>
+          <t>-47,12; 6,46</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,03; 45,5</t>
+          <t>15,99; 44,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 21,14</t>
+          <t>-5,33; 21,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 20,21</t>
+          <t>-5,48; 20,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 25,89</t>
+          <t>-2,81; 24,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-16,5; 10,89</t>
+          <t>-16,17; 11,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 26,09</t>
+          <t>-3,09; 26,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,33; 30,44</t>
+          <t>10,08; 29,82</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 11,93</t>
+          <t>-7,85; 11,93</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 18,74</t>
+          <t>-0,2; 19,09</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>51,28; 307,27</t>
+          <t>58,61; 316,56</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-23,7; 152,18</t>
+          <t>-20,58; 150,59</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-24,22; 135,26</t>
+          <t>-23,2; 140,6</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 77,78</t>
+          <t>-6,21; 72,68</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-34,85; 34,63</t>
+          <t>-35,69; 33,55</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 80,65</t>
+          <t>-7,26; 82,03</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26,95; 116,34</t>
+          <t>26,3; 111,87</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-20,25; 43,95</t>
+          <t>-22,83; 44,66</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 69,35</t>
+          <t>-1,6; 71,74</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-24,63; 4,75</t>
+          <t>-24,86; 3,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-16,25; 11,41</t>
+          <t>-16,9; 10,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-27,95; 4,38</t>
+          <t>-27,78; 2,29</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,72; 28,94</t>
+          <t>-0,87; 27,99</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 24,61</t>
+          <t>-5,54; 23,45</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-29,29; 8,59</t>
+          <t>-26,53; 9,52</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-8,32; 12,77</t>
+          <t>-9,05; 12,02</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-7,62; 13,64</t>
+          <t>-6,78; 14,46</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-21,84; 2,15</t>
+          <t>-23,81; 2,19</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-53,0; 14,83</t>
+          <t>-52,88; 9,49</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-34,73; 34,52</t>
+          <t>-37,39; 32,31</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-62,1; 16,19</t>
+          <t>-62,64; 6,44</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,59; 97,6</t>
+          <t>-1,09; 87,78</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-12,22; 73,59</t>
+          <t>-12,68; 74,13</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-68,3; 23,72</t>
+          <t>-63,25; 25,1</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-19,35; 35,99</t>
+          <t>-21,38; 34,84</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-17,06; 37,4</t>
+          <t>-15,87; 39,93</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-53,62; 3,89</t>
+          <t>-53,73; 6,36</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-37,83; 1,97</t>
+          <t>-40,28; 3,48</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-37,62; 0,58</t>
+          <t>-38,98; -0,04</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-34,14; 1,17</t>
+          <t>-36,31; 1,57</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-32,83; 5,65</t>
+          <t>-34,02; 4,08</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-43,01; -7,99</t>
+          <t>-44,07; -11,08</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-34,01; 2,54</t>
+          <t>-33,55; 2,74</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-30,5; -1,88</t>
+          <t>-29,57; -3,11</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-36,47; -9,34</t>
+          <t>-34,98; -8,81</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-29,45; -3,53</t>
+          <t>-28,29; -2,96</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-62,5; 7,12</t>
+          <t>-66,38; 9,85</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-63,7; -0,93</t>
+          <t>-62,45; 0,69</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-56,43; 3,29</t>
+          <t>-58,07; 3,84</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-48,96; 11,25</t>
+          <t>-50,77; 7,34</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-62,92; -15,73</t>
+          <t>-63,16; -17,53</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-48,99; 3,55</t>
+          <t>-47,48; 5,42</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-47,84; -3,29</t>
+          <t>-48,48; -6,13</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-57,37; -18,16</t>
+          <t>-55,8; -16,91</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-46,21; -7,0</t>
+          <t>-45,6; -6,26</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>4,99; 37,97</t>
+          <t>5,38; 36,24</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 22,11</t>
+          <t>-7,37; 21,49</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-14,02; 15,46</t>
+          <t>-12,75; 16,28</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-27,72; 2,48</t>
+          <t>-28,99; 3,24</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-14,93; 16,31</t>
+          <t>-16,1; 15,43</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-27,47; 2,06</t>
+          <t>-29,03; 1,52</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-8,81; 13,45</t>
+          <t>-10,51; 13,96</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-8,33; 14,22</t>
+          <t>-8,53; 12,77</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-17,58; 3,44</t>
+          <t>-18,16; 3,33</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>12,76; 235,08</t>
+          <t>19,85; 233,1</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-25,73; 125,48</t>
+          <t>-26,27; 126,0</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-46,16; 94,51</t>
+          <t>-42,39; 101,85</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-49,8; 5,54</t>
+          <t>-51,86; 6,75</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-27,14; 38,38</t>
+          <t>-29,21; 36,46</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-49,42; 4,23</t>
+          <t>-50,96; 4,31</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-20,7; 41,36</t>
+          <t>-22,87; 43,68</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-19,99; 43,83</t>
+          <t>-19,45; 40,97</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-41,82; 10,5</t>
+          <t>-41,51; 11,65</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 20,18</t>
+          <t>-1,71; 20,44</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-10,46; 9,61</t>
+          <t>-11,73; 9,2</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 13,91</t>
+          <t>-7,81; 15,31</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4,65; 25,54</t>
+          <t>2,53; 24,05</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-16,35; 4,58</t>
+          <t>-14,95; 5,36</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-10,14; 12,63</t>
+          <t>-9,5; 12,74</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,65; 20,18</t>
+          <t>4,17; 19,39</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-11,17; 3,97</t>
+          <t>-10,74; 3,6</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 10,93</t>
+          <t>-5,39; 10,51</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 82,17</t>
+          <t>-4,55; 83,78</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-30,33; 38,6</t>
+          <t>-32,79; 37,01</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-19,57; 56,65</t>
+          <t>-22,19; 57,67</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>9,67; 72,38</t>
+          <t>6,43; 70,13</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-35,44; 12,53</t>
+          <t>-34,35; 15,51</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-22,97; 36,1</t>
+          <t>-22,25; 35,62</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>12,25; 64,87</t>
+          <t>11,53; 61,88</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-28,51; 12,56</t>
+          <t>-27,53; 11,19</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-12,86; 33,36</t>
+          <t>-13,85; 33,06</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 13,44</t>
+          <t>-6,71; 14,49</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-18,95; 0,64</t>
+          <t>-19,09; -0,14</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-30,15; -11,13</t>
+          <t>-29,43; -10,91</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 17,21</t>
+          <t>-3,58; 17,22</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-11,39; 9,24</t>
+          <t>-10,73; 8,2</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-21,58; -1,83</t>
+          <t>-22,55; -2,35</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 12,81</t>
+          <t>-1,54; 12,38</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-13,59; 1,43</t>
+          <t>-12,51; 1,76</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-23,21; -8,58</t>
+          <t>-23,36; -8,97</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-12,37; 31,73</t>
+          <t>-13,04; 36,01</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-37,87; 1,62</t>
+          <t>-37,77; -0,16</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-59,85; -26,25</t>
+          <t>-59,32; -26,06</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 39,7</t>
+          <t>-6,72; 39,67</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-21,73; 20,53</t>
+          <t>-20,39; 20,41</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-40,79; -3,93</t>
+          <t>-43,3; -5,02</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 29,05</t>
+          <t>-3,08; 28,5</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-26,45; 3,39</t>
+          <t>-24,48; 4,5</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-45,51; -19,46</t>
+          <t>-46,31; -20,32</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>2,04; 11,6</t>
+          <t>1,83; 11,66</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 4,02</t>
+          <t>-5,25; 4,14</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-12,44; -1,78</t>
+          <t>-12,63; -2,38</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>0,19; 9,63</t>
+          <t>0,55; 9,92</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 4,11</t>
+          <t>-5,36; 3,84</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-11,59; -1,2</t>
+          <t>-11,85; -1,55</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,4; 9,1</t>
+          <t>2,56; 9,3</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 3,11</t>
+          <t>-3,83; 2,57</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-10,27; -2,84</t>
+          <t>-10,42; -2,97</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>5,64; 35,67</t>
+          <t>4,78; 34,78</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-13,37; 12,2</t>
+          <t>-14,07; 12,54</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-33,62; -5,68</t>
+          <t>-33,49; -5,96</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>0,52; 22,72</t>
+          <t>1,27; 23,1</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-11,35; 9,58</t>
+          <t>-11,06; 8,93</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-24,39; -2,83</t>
+          <t>-24,43; -3,51</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>5,61; 23,41</t>
+          <t>6,45; 24,29</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-8,93; 7,99</t>
+          <t>-9,11; 6,6</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-24,7; -7,04</t>
+          <t>-24,83; -7,7</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IMC_inf_R2-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IMC_inf_R2-Provincia-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2,82</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11,44</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-17,99</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>9,0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>18,69</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,82</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>11,44</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-18,8</t>
+          <t>1,29</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-9,08</t>
+          <t>-8,54</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 24,48</t>
+          <t>-16,19; 17,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 34,24</t>
+          <t>-5,94; 30,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,09; 16,55</t>
+          <t>-32,89; -1,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,92; 21,53</t>
+          <t>-7,09; 25,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,88; 28,05</t>
+          <t>2,78; 34,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-34,19; -3,9</t>
+          <t>-13,4; 15,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 18,44</t>
+          <t>-5,62; 19,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,77; 25,72</t>
+          <t>2,56; 27,19</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-19,76; 2,02</t>
+          <t>-19,46; 1,65</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>6,63%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>26,88%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-42,29%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>35,29%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>73,3%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>3,91%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>6,63%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>26,88%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-44,19%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-26,6%</t>
+          <t>-25,01%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-23,87; 123,74</t>
+          <t>-32,53; 51,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,3; 181,64</t>
+          <t>-11,97; 89,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-46,66; 85,88</t>
+          <t>-64,79; 0,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-28,22; 69,27</t>
+          <t>-25,35; 139,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-14,45; 85,42</t>
+          <t>6,71; 189,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-67,0; -9,37</t>
+          <t>-42,98; 88,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-14,0; 60,06</t>
+          <t>-15,82; 66,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,83; 89,57</t>
+          <t>6,36; 92,54</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-51,0; 6,92</t>
+          <t>-48,86; 6,54</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-1,94</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5,96</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-3,86</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>3,94</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>5,64</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-9,17</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-1,94</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5,96</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-3,88</t>
+          <t>-4,55</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-7,28</t>
+          <t>-4,33</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,68; 16,32</t>
+          <t>-13,19; 10,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 18,11</t>
+          <t>-5,75; 19,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-27,22; 4,94</t>
+          <t>-17,75; 8,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-13,43; 11,55</t>
+          <t>-7,62; 18,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 17,33</t>
+          <t>-6,91; 17,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-16,97; 10,77</t>
+          <t>-17,03; 7,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-8,7; 9,2</t>
+          <t>-8,29; 9,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 13,99</t>
+          <t>-3,87; 13,92</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-22,12; 2,56</t>
+          <t>-13,5; 5,24</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-3,97%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>12,17%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-7,88%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>11,04%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>15,81%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-25,72%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-3,97%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>12,17%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-7,92%</t>
+          <t>-12,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-16,99%</t>
+          <t>-10,12%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-20,96; 56,95</t>
+          <t>-24,03; 25,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-13,59; 64,28</t>
+          <t>-9,7; 46,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-67,22; 14,29</t>
+          <t>-32,31; 21,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-25,03; 27,34</t>
+          <t>-20,11; 66,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-11,53; 41,56</t>
+          <t>-17,11; 58,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-31,43; 23,81</t>
+          <t>-41,02; 26,63</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-18,35; 23,46</t>
+          <t>-17,9; 23,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 36,38</t>
+          <t>-8,12; 36,37</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-47,12; 6,46</t>
+          <t>-29,26; 14,16</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>11,16</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-2,22</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>10,99</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>29,94</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>7,34</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>6,92</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>11,16</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-2,22</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,03</t>
+          <t>6,85</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9,18</t>
+          <t>8,59</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,99; 44,57</t>
+          <t>-1,82; 24,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 21,91</t>
+          <t>-16,79; 12,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 20,87</t>
+          <t>-3,49; 26,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 24,04</t>
+          <t>16,17; 44,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-16,17; 11,66</t>
+          <t>-6,31; 21,61</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 26,91</t>
+          <t>-6,42; 19,88</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,08; 29,82</t>
+          <t>9,17; 29,82</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,85; 11,93</t>
+          <t>-8,18; 11,64</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 19,09</t>
+          <t>-2,57; 18,39</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>28,06%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-5,58%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>27,66%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>140,05%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>34,31%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>32,36%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>28,06%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-5,58%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>27,7%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>58,61; 316,56</t>
+          <t>-3,78; 74,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-20,58; 150,59</t>
+          <t>-35,23; 35,57</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-23,2; 140,6</t>
+          <t>-7,29; 78,96</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 72,68</t>
+          <t>51,94; 301,31</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-35,69; 33,55</t>
+          <t>-22,76; 144,54</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 82,03</t>
+          <t>-24,66; 135,75</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26,3; 111,87</t>
+          <t>25,06; 113,78</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-22,83; 44,66</t>
+          <t>-23,14; 43,27</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 71,74</t>
+          <t>-7,14; 70,79</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>14,34</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>9,42</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-8,21</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-10,65</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-2,71</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-12,6</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>14,34</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>9,42</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-9,03</t>
+          <t>-13,96</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-10,63</t>
+          <t>-10,84</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-24,86; 3,05</t>
+          <t>0,23; 29,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-16,9; 10,86</t>
+          <t>-4,9; 25,98</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-27,78; 2,29</t>
+          <t>-24,93; 11,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 27,99</t>
+          <t>-24,29; 3,26</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 23,45</t>
+          <t>-17,05; 11,57</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-26,53; 9,52</t>
+          <t>-28,47; 2,07</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-9,05; 12,02</t>
+          <t>-7,75; 11,18</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 14,46</t>
+          <t>-7,49; 12,87</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-23,81; 2,19</t>
+          <t>-22,65; 1,8</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>36,8%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>24,18%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-21,07%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-26,26%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-6,69%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-31,08%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>36,8%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>24,18%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-23,17%</t>
+          <t>-34,42%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-26,78%</t>
+          <t>-27,3%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-52,88; 9,49</t>
+          <t>0,3; 92,9</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-37,39; 32,31</t>
+          <t>-11,51; 81,37</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-62,64; 6,44</t>
+          <t>-59,11; 33,3</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 87,78</t>
+          <t>-52,84; 11,71</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-12,68; 74,13</t>
+          <t>-37,08; 33,69</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-63,25; 25,1</t>
+          <t>-64,01; 6,85</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-21,38; 34,84</t>
+          <t>-17,95; 31,5</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-15,87; 39,93</t>
+          <t>-18,1; 35,89</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-53,73; 6,36</t>
+          <t>-52,13; 5,36</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-14,01</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-26,81</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-14,15</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-19,21</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-18,91</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-17,23</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-14,01</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-26,81</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-15,61</t>
+          <t>-18,39</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-16,2</t>
+          <t>-16,15</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-40,28; 3,48</t>
+          <t>-32,0; 6,07</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-38,98; -0,04</t>
+          <t>-44,53; -10,08</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-36,31; 1,57</t>
+          <t>-30,27; 3,48</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-34,02; 4,08</t>
+          <t>-39,07; 1,61</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-44,07; -11,08</t>
+          <t>-36,76; -1,93</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-33,55; 2,74</t>
+          <t>-36,72; 0,16</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-29,57; -3,11</t>
+          <t>-32,0; -3,73</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-34,98; -8,81</t>
+          <t>-36,07; -10,11</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-28,29; -2,96</t>
+          <t>-28,38; -3,65</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-22,78%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-43,58%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-23,0%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-36,8%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-36,22%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-32,99%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-22,78%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-43,58%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-25,38%</t>
+          <t>-35,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-28,39%</t>
+          <t>-28,31%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-66,38; 9,85</t>
+          <t>-49,11; 11,13</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-62,45; 0,69</t>
+          <t>-64,31; -18,04</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-58,07; 3,84</t>
+          <t>-44,72; 7,45</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-50,77; 7,34</t>
+          <t>-67,87; 2,03</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-63,16; -17,53</t>
+          <t>-60,18; -3,32</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-47,48; 5,42</t>
+          <t>-58,53; 0,99</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-48,48; -6,13</t>
+          <t>-50,47; -7,55</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-55,8; -16,91</t>
+          <t>-57,12; -20,24</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-45,6; -6,26</t>
+          <t>-44,67; -7,1</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-14,37</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-0,53</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>-14,46</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>20,9</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>6,64</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>0,89</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-14,37</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-0,53</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-13,63</t>
+          <t>0,49</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-6,41</t>
+          <t>-7,4</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>5,38; 36,24</t>
+          <t>-29,03; 0,83</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-7,37; 21,49</t>
+          <t>-15,65; 15,94</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-12,75; 16,28</t>
+          <t>-29,34; 1,14</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-28,99; 3,24</t>
+          <t>5,36; 36,98</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-16,1; 15,43</t>
+          <t>-7,9; 22,4</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-29,03; 1,52</t>
+          <t>-12,78; 15,59</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-10,51; 13,96</t>
+          <t>-8,91; 13,85</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-8,53; 12,77</t>
+          <t>-8,22; 13,8</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-18,16; 3,33</t>
+          <t>-18,31; 3,59</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-28,64%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-1,06%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>-28,82%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>86,0%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>27,3%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>3,64%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>-28,64%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>-1,06%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-27,16%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-16,95%</t>
+          <t>-19,58%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>19,85; 233,1</t>
+          <t>-51,65; 2,65</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-26,27; 126,0</t>
+          <t>-28,35; 37,93</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-42,39; 101,85</t>
+          <t>-51,75; 4,17</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-51,86; 6,75</t>
+          <t>13,46; 209,73</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-29,21; 36,46</t>
+          <t>-27,72; 126,79</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-50,96; 4,31</t>
+          <t>-41,37; 85,94</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-22,87; 43,68</t>
+          <t>-20,26; 43,08</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-19,45; 40,97</t>
+          <t>-19,45; 41,77</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-41,51; 11,65</t>
+          <t>-43,19; 10,5</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>14,49</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-5,43</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>2,3</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>9,9</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>-1,0</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>3,79</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>14,49</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-5,43</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,4</t>
+          <t>2,91</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3,0</t>
+          <t>2,96</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 20,44</t>
+          <t>4,78; 25,45</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-11,73; 9,2</t>
+          <t>-15,06; 5,23</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 15,31</t>
+          <t>-8,92; 14,4</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2,53; 24,05</t>
+          <t>-0,38; 20,33</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-14,95; 5,36</t>
+          <t>-10,49; 8,6</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-9,5; 12,74</t>
+          <t>-7,7; 13,02</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,17; 19,39</t>
+          <t>4,67; 19,93</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-10,74; 3,6</t>
+          <t>-10,52; 3,66</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 10,51</t>
+          <t>-5,07; 11,23</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>35,95%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-13,47%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>5,71%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>32,87%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>-3,31%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>12,59%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>35,95%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-13,47%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,4%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 83,78</t>
+          <t>9,53; 73,67</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-32,79; 37,01</t>
+          <t>-33,99; 14,8</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-22,19; 57,67</t>
+          <t>-20,7; 41,28</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6,43; 70,13</t>
+          <t>-1,62; 80,26</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-34,35; 15,51</t>
+          <t>-31,75; 33,9</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-22,25; 35,62</t>
+          <t>-22,15; 52,87</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>11,53; 61,88</t>
+          <t>12,28; 63,5</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-27,53; 11,19</t>
+          <t>-26,97; 10,88</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-13,85; 33,06</t>
+          <t>-13,64; 35,54</t>
         </is>
       </c>
     </row>
@@ -2136,32 +2136,32 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>7,01</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>-1,83</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>-12,44</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>3,62</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>-9,98</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>-20,73</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>7,01</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>-1,83</t>
-        </is>
-      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-12,13</t>
+          <t>-21,89</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-16,01</t>
+          <t>-16,85</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 14,49</t>
+          <t>-2,63; 18,4</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-19,09; -0,14</t>
+          <t>-11,54; 7,98</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-29,43; -10,91</t>
+          <t>-22,03; -1,37</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 17,22</t>
+          <t>-6,46; 13,05</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-10,73; 8,2</t>
+          <t>-20,33; -0,08</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-22,55; -2,35</t>
+          <t>-31,85; -11,8</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 12,38</t>
+          <t>-1,67; 12,5</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-12,51; 1,76</t>
+          <t>-12,61; 1,2</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-23,36; -8,97</t>
+          <t>-23,98; -9,34</t>
         </is>
       </c>
     </row>
@@ -2242,32 +2242,32 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>14,5%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>-3,78%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>-25,72%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>7,85%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>-21,64%</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>-44,95%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>14,5%</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>-3,78%</t>
-        </is>
-      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-25,08%</t>
+          <t>-47,46%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-33,92%</t>
+          <t>-35,71%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-13,04; 36,01</t>
+          <t>-4,99; 42,72</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-37,77; -0,16</t>
+          <t>-22,05; 18,29</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-59,32; -26,06</t>
+          <t>-41,99; -3,79</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 39,67</t>
+          <t>-12,38; 32,91</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-20,39; 20,41</t>
+          <t>-38,76; -0,21</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-43,3; -5,02</t>
+          <t>-62,56; -28,72</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 28,5</t>
+          <t>-3,24; 28,58</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-24,48; 4,5</t>
+          <t>-24,84; 3,04</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-46,31; -20,32</t>
+          <t>-47,63; -21,49</t>
         </is>
       </c>
     </row>
@@ -2352,32 +2352,32 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>5,06</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>-0,69</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>-6,05</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>6,91</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>-0,37</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>-6,91</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>5,06</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>-0,69</t>
-        </is>
-      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-6,42</t>
+          <t>-6,7</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-6,45</t>
+          <t>-6,2</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>1,83; 11,66</t>
+          <t>0,19; 10,03</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 4,14</t>
+          <t>-5,13; 4,46</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-12,63; -2,38</t>
+          <t>-11,69; -1,08</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>0,55; 9,92</t>
+          <t>2,48; 11,51</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 3,84</t>
+          <t>-4,92; 4,31</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-11,85; -1,55</t>
+          <t>-11,13; -2,09</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,56; 9,3</t>
+          <t>2,21; 9,16</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 2,57</t>
+          <t>-3,78; 2,5</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-10,42; -2,97</t>
+          <t>-9,67; -2,94</t>
         </is>
       </c>
     </row>
@@ -2458,32 +2458,32 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>11,15%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>-1,52%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>-13,31%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>19,61%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>-1,04%</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>-19,61%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>11,15%</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>-1,52%</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-14,14%</t>
+          <t>-19,02%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-15,94%</t>
+          <t>-15,32%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>4,78; 34,78</t>
+          <t>0,06; 22,95</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-14,07; 12,54</t>
+          <t>-10,85; 10,07</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-33,49; -5,96</t>
+          <t>-24,75; -2,61</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>1,27; 23,1</t>
+          <t>6,62; 35,38</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-11,06; 8,93</t>
+          <t>-13,21; 13,13</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-24,43; -3,51</t>
+          <t>-29,92; -6,45</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>6,45; 24,29</t>
+          <t>5,25; 23,49</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-9,11; 6,6</t>
+          <t>-9,02; 6,44</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-24,83; -7,7</t>
+          <t>-23,14; -7,25</t>
         </is>
       </c>
     </row>
